--- a/output/身体拘束適正化委員会_議事録_R8.6.25.xlsx
+++ b/output/身体拘束適正化委員会_議事録_R8.6.25.xlsx
@@ -79,7 +79,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -101,11 +101,55 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -135,6 +179,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -500,8 +546,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -509,10 +555,11 @@
     <col width="50" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>令和8年度　身体拘束廃止・適正化委員会　議事録</t>
+          <t>令和8年度　身体拘束適正化委員会　議事録</t>
         </is>
       </c>
     </row>
@@ -523,6 +570,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="24" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -541,8 +589,9 @@
           <t>令和8年6月25日　14時00分～15時00分</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n"/>
-    </row>
+      <c r="D6" s="13" t="n"/>
+    </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -561,8 +610,9 @@
           <t>株式会社dhpケアマネジメント 本社事務所 会議室</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n"/>
-    </row>
+      <c r="D9" s="13" t="n"/>
+    </row>
+    <row r="10"/>
     <row r="11" ht="24" customHeight="1">
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -581,7 +631,7 @@
           <t>生田友哉</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n"/>
+      <c r="D12" s="13" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="4" t="inlineStr">
@@ -594,8 +644,9 @@
           <t>松村知恵、win yadanar aung、吉田俊輔、吉田麻美</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n"/>
-    </row>
+      <c r="D13" s="13" t="n"/>
+    </row>
+    <row r="14"/>
     <row r="15" ht="24" customHeight="1">
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -609,8 +660,8 @@
           <t>1. 身体拘束（身体拘束に該当する行為）の報告状況確認</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="13" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
@@ -618,8 +669,8 @@
           <t>2. 身体拘束廃止・適正化に向けた職員周知・研修状況について</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="13" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="5" t="inlineStr">
@@ -627,8 +678,8 @@
           <t>3. 身体拘束に該当する可能性のある事例共有および予防策の検討</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="13" t="n"/>
     </row>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
@@ -636,9 +687,10 @@
           <t>4. 今後の課題および記録・マニュアル整備について</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-    </row>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="13" t="n"/>
+    </row>
+    <row r="20"/>
     <row r="21" ht="24" customHeight="1">
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -672,7 +724,7 @@
 ・ベッド柵や車いすベルトなどの使用状況も確認したが、身体拘束には該当しない運用であることを確認。</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n"/>
+      <c r="D23" s="13" t="n"/>
     </row>
     <row r="24" ht="64" customHeight="1">
       <c r="B24" s="8" t="inlineStr">
@@ -688,7 +740,7 @@
 ・動画教材等の導入も検討し、理解度の底上げを図る方針。</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n"/>
+      <c r="D24" s="13" t="n"/>
     </row>
     <row r="25" ht="64" customHeight="1">
       <c r="B25" s="8" t="inlineStr">
@@ -704,7 +756,7 @@
 ・本人の生活リズム再評価、観察記録強化、家族との連携強化を決定。</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n"/>
+      <c r="D25" s="13" t="n"/>
     </row>
     <row r="26" ht="64" customHeight="1">
       <c r="B26" s="8" t="inlineStr">
@@ -720,8 +772,9 @@
 ・万が一拘束が必要な場合の医師意見書手順や解除基準については次回協議。</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n"/>
-    </row>
+      <c r="D26" s="13" t="n"/>
+    </row>
+    <row r="27"/>
     <row r="28" ht="24" customHeight="1">
       <c r="B28" s="3" t="inlineStr">
         <is>
@@ -735,8 +788,8 @@
           <t>・必要に応じて臨時開催を行うことを確認。</t>
         </is>
       </c>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="13" t="n"/>
     </row>
     <row r="30">
       <c r="B30" s="5" t="inlineStr">
@@ -744,9 +797,10 @@
           <t>・次回開催は令和8年11月25日頃を予定。</t>
         </is>
       </c>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="6" t="n"/>
-    </row>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="13" t="n"/>
+    </row>
+    <row r="31"/>
     <row r="32" ht="24" customHeight="1">
       <c r="B32" s="3" t="inlineStr">
         <is>
@@ -772,7 +826,7 @@
           <t>確認印： [　　　　　　　　]　　確認日：令和　　年　　月　　日</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n"/>
+      <c r="D34" s="13" t="n"/>
     </row>
     <row r="35" ht="28" customHeight="1">
       <c r="B35" s="11" t="inlineStr">
@@ -785,7 +839,7 @@
           <t>確認印： [　　　　　　　　]　　確認日：令和　　年　　月　　日</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n"/>
+      <c r="D35" s="13" t="n"/>
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="B36" s="11" t="inlineStr">
@@ -798,7 +852,7 @@
           <t>確認印： [　　　　　　　　]　　確認日：令和　　年　　月　　日</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n"/>
+      <c r="D36" s="13" t="n"/>
     </row>
     <row r="37" ht="28" customHeight="1">
       <c r="B37" s="11" t="inlineStr">
@@ -811,7 +865,7 @@
           <t>確認印： [　　　　　　　　]　　確認日：令和　　年　　月　　日</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n"/>
+      <c r="D37" s="13" t="n"/>
     </row>
     <row r="38" ht="28" customHeight="1">
       <c r="B38" s="11" t="inlineStr">
@@ -824,7 +878,7 @@
           <t>確認印： [　　　　　　　　]　　確認日：令和　　年　　月　　日</t>
         </is>
       </c>
-      <c r="D38" s="6" t="n"/>
+      <c r="D38" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="30">

--- a/output/身体拘束適正化委員会_議事録_R8.6.25.xlsx
+++ b/output/身体拘束適正化委員会_議事録_R8.6.25.xlsx
@@ -546,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="B2:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -555,7 +555,6 @@
     <col width="50" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -566,11 +565,10 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>（株式会社dhpケアマネジメント）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
+          <t>（株式会社dhpケアマネジメント　いいかいご）</t>
+        </is>
+      </c>
+    </row>
     <row r="5" ht="24" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -591,7 +589,6 @@
       </c>
       <c r="D6" s="13" t="n"/>
     </row>
-    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -612,7 +609,6 @@
       </c>
       <c r="D9" s="13" t="n"/>
     </row>
-    <row r="10"/>
     <row r="11" ht="24" customHeight="1">
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -646,7 +642,6 @@
       </c>
       <c r="D13" s="13" t="n"/>
     </row>
-    <row r="14"/>
     <row r="15" ht="24" customHeight="1">
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -690,7 +685,6 @@
       <c r="C19" s="14" t="n"/>
       <c r="D19" s="13" t="n"/>
     </row>
-    <row r="20"/>
     <row r="21" ht="24" customHeight="1">
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -752,7 +746,7 @@
       <c r="C25" s="9" t="inlineStr">
         <is>
           <t>・認知症進行による夜間不穏がある利用者について事例共有。
-・徘徊・転倒リスクに対し、環境整備や巡視頻度見直しなど拘束に頼らない予防策を検討。
+・徘徊・転倒リスクに対し、環境整備や、訪問時の見守り強化・訪問回数や時間帯の見直し（ケアマネジャーと相談）など拘束に頼らない予防策を検討。
 ・本人の生活リズム再評価、観察記録強化、家族との連携強化を決定。</t>
         </is>
       </c>
@@ -774,7 +768,6 @@
       </c>
       <c r="D26" s="13" t="n"/>
     </row>
-    <row r="27"/>
     <row r="28" ht="24" customHeight="1">
       <c r="B28" s="3" t="inlineStr">
         <is>
@@ -800,7 +793,6 @@
       <c r="C30" s="14" t="n"/>
       <c r="D30" s="13" t="n"/>
     </row>
-    <row r="31"/>
     <row r="32" ht="24" customHeight="1">
       <c r="B32" s="3" t="inlineStr">
         <is>

--- a/output/身体拘束適正化委員会_議事録_R8.6.25.xlsx
+++ b/output/身体拘束適正化委員会_議事録_R8.6.25.xlsx
@@ -546,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D38"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -555,6 +555,7 @@
     <col width="50" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -569,6 +570,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="24" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -589,6 +591,7 @@
       </c>
       <c r="D6" s="13" t="n"/>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -609,6 +612,7 @@
       </c>
       <c r="D9" s="13" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11" ht="24" customHeight="1">
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -637,11 +641,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>松村知恵、win yadanar aung、吉田俊輔、吉田麻美</t>
+          <t>松村知恵、WIN YADANAR AUNG、吉田俊輔、吉田麻美</t>
         </is>
       </c>
       <c r="D13" s="13" t="n"/>
     </row>
+    <row r="14"/>
     <row r="15" ht="24" customHeight="1">
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -685,6 +690,7 @@
       <c r="C19" s="14" t="n"/>
       <c r="D19" s="13" t="n"/>
     </row>
+    <row r="20"/>
     <row r="21" ht="24" customHeight="1">
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -768,6 +774,7 @@
       </c>
       <c r="D26" s="13" t="n"/>
     </row>
+    <row r="27"/>
     <row r="28" ht="24" customHeight="1">
       <c r="B28" s="3" t="inlineStr">
         <is>
@@ -793,6 +800,7 @@
       <c r="C30" s="14" t="n"/>
       <c r="D30" s="13" t="n"/>
     </row>
+    <row r="31"/>
     <row r="32" ht="24" customHeight="1">
       <c r="B32" s="3" t="inlineStr">
         <is>
@@ -836,7 +844,7 @@
     <row r="36" ht="28" customHeight="1">
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>win yadanar aung（委員）</t>
+          <t>WIN YADANAR AUNG（委員）</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">

--- a/output/身体拘束適正化委員会_議事録_R8.6.25.xlsx
+++ b/output/身体拘束適正化委員会_議事録_R8.6.25.xlsx
@@ -641,7 +641,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>松村知恵、WIN YADANAR AUNG、吉田俊輔、吉田麻美</t>
+          <t>松村知恵、WIN YADANAR AUNG、吉田駿成、吉田麻美</t>
         </is>
       </c>
       <c r="D13" s="13" t="n"/>
@@ -857,7 +857,7 @@
     <row r="37" ht="28" customHeight="1">
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>吉田俊輔（委員）</t>
+          <t>吉田駿成（委員）</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">

--- a/output/身体拘束適正化委員会_議事録_R8.6.25.xlsx
+++ b/output/身体拘束適正化委員会_議事録_R8.6.25.xlsx
@@ -544,9 +544,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="B2:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -555,7 +555,6 @@
     <col width="50" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -570,7 +569,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -591,7 +589,6 @@
       </c>
       <c r="D6" s="13" t="n"/>
     </row>
-    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -612,7 +609,6 @@
       </c>
       <c r="D9" s="13" t="n"/>
     </row>
-    <row r="10"/>
     <row r="11" ht="24" customHeight="1">
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -646,7 +642,6 @@
       </c>
       <c r="D13" s="13" t="n"/>
     </row>
-    <row r="14"/>
     <row r="15" ht="24" customHeight="1">
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -690,7 +685,6 @@
       <c r="C19" s="14" t="n"/>
       <c r="D19" s="13" t="n"/>
     </row>
-    <row r="20"/>
     <row r="21" ht="24" customHeight="1">
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -774,7 +768,6 @@
       </c>
       <c r="D26" s="13" t="n"/>
     </row>
-    <row r="27"/>
     <row r="28" ht="24" customHeight="1">
       <c r="B28" s="3" t="inlineStr">
         <is>
@@ -800,7 +793,6 @@
       <c r="C30" s="14" t="n"/>
       <c r="D30" s="13" t="n"/>
     </row>
-    <row r="31"/>
     <row r="32" ht="24" customHeight="1">
       <c r="B32" s="3" t="inlineStr">
         <is>
@@ -913,6 +905,8 @@
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="B2:D2"/>
   </mergeCells>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>